--- a/20260630/yes24_검색결과.xlsx
+++ b/20260630/yes24_검색결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,725 +456,749 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>세계 문화 여행 - 사우디아라비아</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-셰릴 오발 저/이주현 역
-                            </t>
-        </is>
-      </c>
+          <t>[YES24배송]교육용 보드게임_고피쉬 시리즈 Best 40</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10,500</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>시그마북스</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2025년 03월</t>
-        </is>
-      </c>
+          <t>YES24발송 GIFT상품/행복한바오밥</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>imgaes\yes24\세계 문화 여행 - 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\[YES24배송]교육용 보드게임_고피쉬 시리즈 Best 40.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>떨기나무</t>
+          <t>혼자서도 잘하는 첫  한글 쓰기 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">
-김승학 저
+길벗놀이학습연구소 저/김희정 그림
                             </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>6,750</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>두란노</t>
+          <t>길벗스쿨</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2007년 05월</t>
+          <t>2025년 01월</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>imgaes\yes24\떨기나무.jpg</t>
+          <t>imgaes\yes24\혼자서도 잘하는 첫  한글 쓰기 1.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>행복한 주스나무</t>
+          <t>혼자서도 잘하는 첫  한글 쓰기 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">
-공경희 역
+길벗놀이학습연구소 저/김희정 그림
                             </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10,800</t>
+          <t>6,750</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>찰리북</t>
+          <t>길벗스쿨</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2011년 02월</t>
+          <t>2025년 01월</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>imgaes\yes24\행복한 주스나무.jpg</t>
+          <t>imgaes\yes24\혼자서도 잘하는 첫  한글 쓰기 2.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>세계 문화 여행 - 사우디아라비아</t>
+          <t>재미있고 빠른 첫 한글 쓰기 2 가나다 글자</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">
-셰릴 오발 저/이주현 역
+한빛학습연구회 글/김희선 그림
                             </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>5,850</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>시그마북스</t>
+          <t>한빛에듀</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025년 03월</t>
+          <t>2021년 05월</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>imgaes\yes24\세계 문화 여행 - 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\재미있고 빠른 첫 한글 쓰기 2 가나다 글자.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>세상에 문을 연 사우디아라비아</t>
+          <t>가나다는 맛있다</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">
-김경곤, 장은경 저
+우지영 글/김은재 그림
                             </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16,500</t>
+          <t>10,800</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BOOKK(부크크)</t>
+          <t>책읽는곰</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025년 06월</t>
+          <t>2016년 09월</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>imgaes\yes24\세상에 문을 연 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\가나다는 맛있다.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>유해한 관계로부터 나를 지키는 법</t>
+          <t>가나다 글자 놀이</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">
-샤히다 아라비 저/이시은 역
+이상교 글/밤코 그림
                             </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>14,400</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>문학동네</t>
+          <t>한솔수북</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2022년 11월</t>
+          <t>2024년 12월</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>imgaes\yes24\유해한 관계로부터 나를 지키는 법.jpg</t>
+          <t>imgaes\yes24\가나다 글자 놀이.jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>지금 다시, 사우디아라비아</t>
+          <t>뭐든지 나라의 가나다</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">
-박인식 저
+박지윤 글그림
                             </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16,200</t>
+          <t>13,500</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>동아시아</t>
+          <t>보림</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2024년 03월</t>
+          <t>2020년 12월</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>imgaes\yes24\지금 다시, 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\뭐든지 나라의 가나다.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>사우디아라비아 지도 뱃지</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>new 가나다 KOREAN for Japanese 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+가나다 한국어학원 저
+                            </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>로고마크(logomark)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>한글파크</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2010년 08월</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아 지도 뱃지.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Japanese 1.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>사우디아라비아 뱃지 컬렉션</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>한글 재미 그림책 놀자! 가나다</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+김세실 글/이혜영 그림
+                            </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7,000</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>10,450</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>한빛에듀</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2021년 02월</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아 뱃지 컬렉션.jpg</t>
+          <t>imgaes\yes24\한글 재미 그림책 놀자! 가나다.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>이븐 아라비 아포리즘 나를 알면 우주가 보인다</t>
+          <t>재미있고 빠른 첫 한글 쓰기 1~2권 세트</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">
-루미너리북스 인문출판 에디팅 팀 저
+한빛학습연구회 글/김희선 그림
                             </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8,010</t>
+          <t>11,700</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>루미너리북스</t>
+          <t>한빛에듀</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025년 10월</t>
+          <t>2021년 05월</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>imgaes\yes24\이븐 아라비 아포리즘 나를 알면 우주가 보인다.jpg</t>
+          <t>imgaes\yes24\재미있고 빠른 첫 한글 쓰기 1~2권 세트.jpg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>유해한 관계로부터 나를 지키는 법</t>
+          <t>첫공부 한글 스티커 : 가나다</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">
-샤히다 아라비 저/이시은 역
+가치교육연구소 글
                             </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12,800</t>
+          <t>11,520</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>문학동네</t>
+          <t>가치잇다</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2022년 12월</t>
+          <t>2024년 11월</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>imgaes\yes24\유해한 관계로부터 나를 지키는 법.jpg</t>
+          <t>imgaes\yes24\첫공부 한글 스티커  가나다.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>사우디아라비아 통치기본법</t>
+          <t>누리과정 또박또박 첫 한글쓰기 : 2단계 가나다 원리한글</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">
-김종도, 정상률, 임병필, 박현도 공편 / 명지대학교 중동문제연구소 기획
+                                편집부 저
                             </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>6,120</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>모시는사람들</t>
+          <t>루덴스</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2016년 05월</t>
+          <t>2025년 02월</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아 통치기본법.jpg</t>
+          <t>imgaes\yes24\누리과정 또박또박 첫 한글쓰기  2단계 가나다 원리한글.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>지금은 라마단 (세이펜 적용, 세이펜 미포함)</t>
+          <t>재미있고 빠른 읽기 떼는 동화 가나다 글자</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">
-허지훈 글 / 김희영 그림
+김세실 글/이선주 그림
                             </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11,700</t>
+          <t>10,800</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>누리</t>
+          <t>한빛에듀</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025년 02월</t>
+          <t>2019년 06월</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>imgaes\yes24\지금은 라마단 (세이펜 적용, 세이펜 미포함).jpg</t>
+          <t>imgaes\yes24\재미있고 빠른 읽기 떼는 동화 가나다 글자.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>On Saudi Arabia: Its People, Past, Religion, Fault Lines--And Future</t>
+          <t>new 가나다 KOREAN for Foreigners 2 Elementary WORKBOOK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">
-캐런 엘리엇 하우스 저
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31,770</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Knopf Doubleday Publishing Group</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2013년 06월</t>
+          <t>2011년 01월</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>imgaes\yes24\On Saudi Arabia Its People, Past, Religion, Fault Lines--And Future.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Foreigners 2 Elementary WORKBOOK.jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>세상에 문을 연 사우디아라비아</t>
+          <t>춤추는 가나다라</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">
-김경곤, 장은경 저
+이달 글/강혜숙 그림/김성미 편
                             </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11,500</t>
+          <t>13,500</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>부크크</t>
+          <t xml:space="preserve">달달북스 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025년 06월</t>
+          <t>2023년 11월</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>imgaes\yes24\세상에 문을 연 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\춤추는 가나다라.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>중동&amp;아프리카 국기 지도 뱃지 컬렉션</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>new 가나다 KOREAN for Japanese 2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+가나다 한국어학원 저
+                            </t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>로고마크(logomark)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>한글파크</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2011년 01월</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>imgaes\yes24\중동&amp;아프리카 국기 지도 뱃지 컬렉션.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Japanese 2.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>디베르티멘토 (1Disc)</t>
+          <t>new 가나다 KOREAN for Japanese 1,2권 세트</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">
-마리카스티유 망시옹샤르 감독/울라야 아맘라, 리나 엘 아라비, Niels Arestrup 출연
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24,500</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>인조인간</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025년 03월</t>
+          <t>2011년 01월</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>imgaes\yes24\디베르티멘토 (1Disc).jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Japanese 1,2권 세트.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2019 국별 진출전략 사우디아라비아</t>
+          <t>new 가나다 KOREAN for Foreigners 1 Elementary WORKBOOK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">
-대한무역투자진흥공사 저
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2020년 01월</t>
+          <t>2010년 10월</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>imgaes\yes24\2019 국별 진출전략 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Foreigners 1 Elementary WORKBOOK.jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>사우디아라비아 취업 및 창업 가이드</t>
+          <t>가나다 점프</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">
-대한무역투자진흥공사 저
+한라경 글/강은옥 그림
                             </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>보랏빛소어린이</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2020년 01월</t>
+          <t>2025년 06월</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아 취업 및 창업 가이드.jpg</t>
+          <t>imgaes\yes24\가나다 점프.jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>세계국기교차뱃지1</t>
+          <t>엄마가 골라주는 가나다 한글 2 첫걸음</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">
-                                뱃지
+BIG PICTURE 글
                             </t>
         </is>
       </c>
@@ -1185,1010 +1209,2045 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>로고마크(logomark)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>랭컴(LanCom)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2023년 06월</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>imgaes\yes24\세계국기교차뱃지1.jpg</t>
+          <t>imgaes\yes24\엄마가 골라주는 가나다 한글 2 첫걸음.jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>세계 탁상기 모음(한국,사우디아라비아,인도,일본)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>첫공부 한글 쓰기 : 가나다</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+가치교육연구소 글
+                            </t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14,000</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+          <t>8,820</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>가치잇다</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2024년 11월</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>imgaes\yes24\세계 탁상기 모음(한국,사우디아라비아,인도,일본).jpg</t>
+          <t>imgaes\yes24\첫공부 한글 쓰기  가나다.jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[The Bella] 칸딘스키 - 아라비아 I (아라비아의 묘지) Arabs I (Arabian Cemetery) 모던프레임 캔버스액자</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>도시 가나다</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+윤정미 글그림
+                            </t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18,200</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The Bella(더벨라)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2022년 09월</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>imgaes\yes24\[The Bella] 칸딘스키 - 아라비아 I (아라비아의 묘지) Arabs I (Arabian Cemetery) 모던프레임 캔버스액자.jpg</t>
+          <t>imgaes\yes24\도시 가나다.jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>위민 투 드라이브</t>
+          <t>New 가나다 KOREAN 고급1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
           <t xml:space="preserve">
-마날 알샤리프 저/김희숙 역
+가나다한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11,200</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>혜윰터</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2021년 04월</t>
+          <t>2017년 06월</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>imgaes\yes24\위민 투 드라이브.jpg</t>
+          <t>imgaes\yes24\New 가나다 KOREAN 고급1.jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>사우디아라비아</t>
+          <t>가나다 아저씨 (빅북)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">
-이원삼 저
+김수희 글/유하영 그림
                             </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>선문대학교출판부</t>
+          <t>크레용하우스</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2015년 03월</t>
+          <t>2018년 02월</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아.jpg</t>
+          <t>imgaes\yes24\가나다 아저씨 (빅북).jpg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>지금 다시, 사우디아라비아</t>
+          <t>쉽고 빠르게 익히는 가나다 쓰기</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
           <t xml:space="preserve">
-박인식 저
+어린이교육연구원 글
                             </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12,600</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>동아시아</t>
+          <t>효리원</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024년 03월</t>
+          <t>2026년 02월</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>imgaes\yes24\지금 다시, 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\쉽고 빠르게 익히는 가나다 쓰기.jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>위민 투 드라이브</t>
+          <t>염소똥 가나다</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
           <t xml:space="preserve">
-마날 알샤리프 저/김희숙 역
+이나래 저
                             </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>14,400</t>
+          <t>15,120</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>혜윰터</t>
+          <t>반달(킨더랜드)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2021년 04월</t>
+          <t>2017년 07월</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>imgaes\yes24\위민 투 드라이브.jpg</t>
+          <t>imgaes\yes24\염소똥 가나다.jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>세계각국의 국기교차 뱃지 (한국-사우디아라비아)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>엄마가 골라주는 가나다 한글 3 첫걸음</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+BIG PICTURE 저
+                            </t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>9,000</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>랭컴(LanCom)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2023년 07월</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>imgaes\yes24\세계각국의 국기교차 뱃지 (한국-사우디아라비아).jpg</t>
+          <t>imgaes\yes24\엄마가 골라주는 가나다 한글 3 첫걸음.jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>세계각국의 휘날리는 국기뱃지 시리즈2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>엄마가 골라주는 가나다 한글 첫걸음 세트</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+BIG PICTURE 저
+                            </t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>로고마크(logomark)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>랭컴(LanCom)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2023년 07월</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>imgaes\yes24\세계각국의 휘날리는 국기뱃지 시리즈2.jpg</t>
+          <t>imgaes\yes24\엄마가 골라주는 가나다 한글 첫걸음 세트.jpg</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>사우디아라비아 투자 실무 가이드</t>
+          <t>재미있고 빠른 첫 한글 3 가나다</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
           <t xml:space="preserve">
-KOTRA 저
+한빛학습연구회 글 / 김희선 그림
                             </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5,850</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>한빛에듀</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2019년 03월</t>
+          <t>2019년 02월</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아 투자 실무 가이드.jpg</t>
+          <t>imgaes\yes24\재미있고 빠른 첫 한글 3 가나다.jpg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>사우디아라비아 여성운전 허용 결정, 현지 반응과 시사점</t>
+          <t>New 가나다 KOREAN for Foreigners 고급 2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
           <t xml:space="preserve">
-KOTRA 저
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2017년 10월</t>
+          <t>2018년 09월</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아 여성운전 허용 결정, 현지 반응과 시사점.jpg</t>
+          <t>imgaes\yes24\New 가나다 KOREAN for Foreigners 고급 2.jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>신앙 김밥 : 이란과 이라크와 사우디아라비아</t>
+          <t>new 가나다 KOREAN for Foreigners 1 Elementary</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
           <t xml:space="preserve">
-바이블 스터디 저
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>미디어 북</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2018년 11월</t>
+          <t>2010년 08월</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>imgaes\yes24\신앙 김밥  이란과 이라크와 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Foreigners 1 Elementary.jpg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>행복한 주스나무</t>
+          <t>new 가나다 KOREAN for Foreigners 1 Elementary+WORKBOOK 세트</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
           <t xml:space="preserve">
-공경희 역
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8,400</t>
+          <t>32,400</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>찰리북</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2023년 07월</t>
+          <t>2010년 10월</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>imgaes\yes24\행복한 주스나무.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Foreigners 1 Elementary+WORKBOOK 세트.jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>디자인으로 배우는 GO! GLOBAL 시리즈 (전 6권) - 캐나다/인도/이탈리아/사우디아라비아/러시아/아르헨티나</t>
+          <t>가나다 아저씨</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
           <t xml:space="preserve">
-                                gumbook 그림
+김수희 글/유하영 그림
                             </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25,920</t>
+          <t>10,800</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>아메바(amoeba)</t>
+          <t>크레용하우스</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2010년 11월</t>
+          <t>2016년 12월</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>imgaes\yes24\디자인으로 배우는 GO! GLOBAL 시리즈 (전 6권) - 캐나다인도이탈리아사우디아라비아러시아아르헨티나.jpg</t>
+          <t>imgaes\yes24\가나다 아저씨.jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>국가정보 사우디아라비아</t>
+          <t>new 가나다 KOREAN for Foreigners 2 Elementary</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
           <t xml:space="preserve">
-KOTRA 편
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>41,000</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>코트라(KOTRA)</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2018년 03월</t>
+          <t>2011년 01월</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>imgaes\yes24\국가정보 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Foreigners 2 Elementary.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>롤리팝 세계문화 10 지금은 라마단 (사우디아라비아)</t>
+          <t>New 가나다 KOREAN 워크북 고급1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
           <t xml:space="preserve">
-허지훈 글 / 김희영 그림
+가나다한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8,550</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>㈜이수미디어</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2016년 06월</t>
+          <t>2017년 07월</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>imgaes\yes24\롤리팝 세계문화 10 지금은 라마단 (사우디아라비아).jpg</t>
+          <t>imgaes\yes24\New 가나다 KOREAN 워크북 고급1.jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>사우디아라비아 외 5개국</t>
+          <t>new 가나다 KOREAN for Japanese 중급 2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
           <t xml:space="preserve">
-석영섭 글 / 이만수 그림
+가나다한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11,400</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>한국헤르만헤세</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2017년 08월</t>
+          <t>2013년 05월</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아 외 5개국.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Japanese 중급 2.jpg</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>사우디아라비아</t>
+          <t>new 가나다 KOREAN for Chinese 중급 1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
           <t xml:space="preserve">
-캐런 엘리엇 하우스 저/서정민 해제
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>메디치미디어</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2016년 08월</t>
+          <t>2012년 01월</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Chinese 중급 1.jpg</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Flame Of Araby (아라비) (DVD-R)(한글무자막)(DVD)</t>
+          <t>new 가나다 KOREAN for Chinese 1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">
-Maureen O′Hara, Jeff Chandler
-</t>
+가나다 한국어학원 저
+                            </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>44,800</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>22,500</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한글파크</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2014년 09월</t>
+          <t>2010년 08월</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>imgaes\yes24\Flame Of Araby (아라비) (DVD-R)(한글무자막)(DVD).jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Chinese 1.jpg</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>신흥교역국의 통관환경 연구 사우디아라비아</t>
+          <t>[빅북] 뭐든지 나라의 가나다</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
           <t xml:space="preserve">
-한국조세재정연구원 저
+박지윤 글그림
                             </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>휴먼컬처아리랑</t>
+          <t>보림</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2014년 09월</t>
+          <t>2021년 09월</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>imgaes\yes24\신흥교역국의 통관환경 연구 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\[빅북] 뭐든지 나라의 가나다.jpg</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>초대형 아날로그 프로젝션 시계 - 아라비아체</t>
+          <t>new 가나다 KOREAN for Chinese 중급 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
           <t xml:space="preserve">
-                                초대형 아날로그 프로젝션 시계 - 아라비아체
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>112,000</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>디자인에버/디자인에버</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>한글파크</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2013년 06월</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>imgaes\yes24\초대형 아날로그 프로젝션 시계 - 아라비아체.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Chinese 중급 2.jpg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>사우디아라비아 통치기본법</t>
+          <t>new 가나다 KOREAN for Foreigners 2 Intermediate</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
           <t xml:space="preserve">
-김종도, 정상률, 박현도, 안정국 공역 / 명지대학교 중동문제연구소 기획
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7,200</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>모시는사람들</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2013년 06월</t>
+          <t>2013년 04월</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아 통치기본법.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Foreigners 2 Intermediate.jpg</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>사우디아라비아</t>
+          <t>new 가나다 KOREAN for Foreigners 1 Intermediate</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
           <t xml:space="preserve">
-gumbook 그림
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4,320</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>아메바(amoeba)</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2010년 11월</t>
+          <t>2011년 11월</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>imgaes\yes24\사우디아라비아.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Foreigners 1 Intermediate.jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>국가정보 사우디아라비아</t>
+          <t>new 가나다 KOREAN for Chinese 2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
           <t xml:space="preserve">
-KOTRA 편
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>41,000</t>
+          <t>22,500</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>코트라(KOTRA)</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2010년 01월</t>
+          <t>2011년 01월</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>imgaes\yes24\국가정보 사우디아라비아.jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Chinese 2.jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Eduardo Paniagua 알-안달루스의 샘 - 엘 아라비 앙상블 &amp; 파니아구아 베스트 (Agua de Al-Andalus - Best)</t>
+          <t>new 가나다 KOREAN for Chinese 1,2 권세트</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
           <t xml:space="preserve">
-Eduardo Paniagua
-</t>
+가나다 한국어학원 저
+                            </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pneuma</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2008년 06월</t>
+          <t>2011년 01월</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>imgaes\yes24\Eduardo Paniagua 알-안달루스의 샘 - 엘 아라비 앙상블 &amp; 파니아구아 베스트 (Agua de Al-Andalus - Best).jpg</t>
+          <t>imgaes\yes24\new 가나다 KOREAN for Chinese 1,2 권세트.jpg</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>지식똑똑 지구촌 사회·문화 탐구 14</t>
+          <t>New 가나다 KOREAN for Foreigners 워크북 고급 2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
           <t xml:space="preserve">
-서경석 글 / 황재모 그림
+가나다 한국어학원 저
                             </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11,520</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>한국헤르만헤세(Korea Hermannhesse)</t>
+          <t>한글파크</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2014년 05월</t>
+          <t>2018년 09월</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>imgaes\yes24\지식똑똑 지구촌 사회·문화 탐구 14.jpg</t>
+          <t>imgaes\yes24\New 가나다 KOREAN for Foreigners 워크북 고급 2.jpg</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>암을 이기는 듀얼면역요법</t>
+          <t>가나다 소풍</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
           <t xml:space="preserve">
-양억관 역
+문채빈 글그림
                             </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6,300</t>
+          <t>13,500</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>호도애</t>
+          <t>웅진주니어</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2003년 10월</t>
+          <t>2024년 10월</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>imgaes\yes24\암을 이기는 듀얼면역요법.jpg</t>
+          <t>imgaes\yes24\가나다 소풍.jpg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>아라비따</t>
+          <t>가나다</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>술타나</t>
+          <t>콕콕콕 사운드 벽보 : 가나다</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
           <t xml:space="preserve">
-                                진 세손 저 / 이영선 역
+키움 편집부 저
                             </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7,650</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>문학세계사</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2002년 05월</t>
+          <t>2022년 02월</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>imgaes\yes24\술타나.jpg</t>
+          <t>imgaes\yes24\콕콕콕 사운드 벽보  가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>랄랄라 사운드 벽보 3 가나다</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>아이키움북</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2017년 10월</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\랄랄라 사운드 벽보 3 가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>냠냠 한글 가나다</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+정낙묵 글/이제호, 장순일 그림/이주영 감수
+                            </t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>10,800</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>고인돌</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2019년 04월</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\냠냠 한글 가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>한글퍼즐 가나다 8절 퍼즐</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5,250</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>새샘</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026년 03월</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\한글퍼즐 가나다 8절 퍼즐.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>한글 가나다</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2012년 11월</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\한글 가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>별초롱 사운드 벽그림 가나다 한글2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>그린키즈</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2016년 12월</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\별초롱 사운드 벽그림 가나다 한글2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>첫공부 한글 숨은그림찾기 : 가나다</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+가치교육연구소 글
+                            </t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8,820</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>가치잇다</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2024년 11월</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\첫공부 한글 숨은그림찾기  가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>낱말카드 색칠북 : 가나다</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+이정민 저
+                            </t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>당근북스</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2021년 03월</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\낱말카드 색칠북  가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>가나다 한글</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4,950</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>키움</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2023년 10월</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\가나다 한글.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>룰루랄라 사운드 벽보 쏙쏙 가나다</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4,550</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>새샘</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2022년 03월</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\룰루랄라 사운드 벽보 쏙쏙 가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>별초롱 사운드 벽그림 가나다 한글1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>그린키즈</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2016년 12월</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\별초롱 사운드 벽그림 가나다 한글1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>new 가나다 KOREAN for Foreigners 2 Intermediate WORKBOOK</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+GANADA Korean Language Institute 저
+                            </t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>9,900</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한글파크</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2013년 04월</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\new 가나다 KOREAN for Foreigners 2 Intermediate WORKBOOK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>new 가나다 KOREAN for Japanese 중급 1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>22,500</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한글파크</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2012년 01월</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\new 가나다 KOREAN for Japanese 중급 1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>글짓기는 가나다 논설문</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+한국소설대학 편
+                            </t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>자유지성사</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2015년 04월</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\글짓기는 가나다 논설문.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>한글 가나다</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4,320</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>어린왕자</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2023년 10월</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\한글 가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>소퍼즐 가나다 한글</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+                                편집부 저
+                            </t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>지원</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2023년 06월</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\소퍼즐 가나다 한글.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>말자루 글자루 60 라랄라라 가나다</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+김수영 글 / 김순영 그림
+                            </t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>9,500</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한국헤르만헤세(Korea Hermannhesse)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2018년 01월</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\말자루 글자루 60 라랄라라 가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>또박또박 읽고 써요 가나다 + 123</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+이상교 글그림
+                            </t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>24,300</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>책모종</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2023년 04월</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\또박또박 읽고 써요 가나다 + 123.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>글짓기는 가나다 동화</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+한국소설대학 편저
+                            </t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>자유지성사</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2016년 11월</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\글짓기는 가나다 동화.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>글짓기는 가나다 기행문</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+한국소설대학 편저
+                            </t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>자유지성사</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2016년 11월</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\글짓기는 가나다 기행문.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>글짓기는 가나다 동극·희곡</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+한국소설대학 편저
+                            </t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>자유지성사</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2016년 10월</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\글짓기는 가나다 동극·희곡.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>글짓기는 가나다 관찰기록문</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+한국소설대학 편
+                            </t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>자유지성사</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2016년 10월</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\글짓기는 가나다 관찰기록문.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>글짓기는 가나다 편지글</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+한국소설대학 편
+                            </t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>자유지성사</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2016년 10월</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\글짓기는 가나다 편지글.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>가나다 한글교본 쓰기</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+홍솔 글그림
+                            </t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>나무와가지</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2016년 10월</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\가나다 한글교본 쓰기.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+조준철 그림
+                            </t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>별똥별</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2022년 12월</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\가나다.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>가나다</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>글짓기는 가나다 독서감상문</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+한국소설대학 편저
+                            </t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>자유지성사</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2017년 05월</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>imgaes\yes24\글짓기는 가나다 독서감상문.jpg</t>
         </is>
       </c>
     </row>
